--- a/Cargue productos/Menu Web.xlsx
+++ b/Cargue productos/Menu Web.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -744,7 +744,7 @@
         <v>Panadería</v>
       </c>
       <c r="B21" t="str">
-        <v>Pastel americano</v>
+        <v>Horneado americano</v>
       </c>
       <c r="C21" t="str">
         <v>.</v>
@@ -761,7 +761,7 @@
         <v>Panadería</v>
       </c>
       <c r="B22" t="str">
-        <v>Pastel de carne</v>
+        <v>Horneado de carne</v>
       </c>
       <c r="C22" t="str">
         <v>.</v>
@@ -778,7 +778,7 @@
         <v>Panadería</v>
       </c>
       <c r="B23" t="str">
-        <v>Pastel italiano</v>
+        <v>Horneado italiano</v>
       </c>
       <c r="C23" t="str">
         <v>.</v>
@@ -795,7 +795,7 @@
         <v>Panadería</v>
       </c>
       <c r="B24" t="str">
-        <v>Pastel Hawaiano</v>
+        <v>Horneado Hawaiano</v>
       </c>
       <c r="C24" t="str">
         <v>.</v>
@@ -1230,19 +1230,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Sodas Italianas</v>
+        <v>Vinos</v>
       </c>
       <c r="B51" t="str">
-        <v>SODA ITALIANA DE LYCHEE</v>
+        <v>TINTO DE VERANO - JARRA</v>
       </c>
       <c r="C51" t="str">
         <v>.</v>
       </c>
       <c r="D51">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="F51" t="str">
-        <v>images/productos/1583 menu/LYCHEE.jpg</v>
+        <v>images/productos/1583 menu/Jarra Sangria.JPG</v>
       </c>
     </row>
     <row r="52">
@@ -1250,13 +1250,13 @@
         <v>Vinos</v>
       </c>
       <c r="B52" t="str">
-        <v>TINTO DE VERANO - JARRA</v>
+        <v>TINTO DE VERANO - MEDIA JARRA</v>
       </c>
       <c r="C52" t="str">
         <v>.</v>
       </c>
       <c r="D52">
-        <v>75000</v>
+        <v>32500</v>
       </c>
       <c r="F52" t="str">
         <v>images/productos/1583 menu/Jarra Sangria.JPG</v>
@@ -1267,13 +1267,13 @@
         <v>Vinos</v>
       </c>
       <c r="B53" t="str">
-        <v>TINTO DE VERANO - MEDIA JARRA</v>
+        <v xml:space="preserve"> TINTO DE VERANO - COPA</v>
       </c>
       <c r="C53" t="str">
         <v>.</v>
       </c>
       <c r="D53">
-        <v>32500</v>
+        <v>18000</v>
       </c>
       <c r="F53" t="str">
         <v>images/productos/1583 menu/Jarra Sangria.JPG</v>
@@ -1284,16 +1284,16 @@
         <v>Vinos</v>
       </c>
       <c r="B54" t="str">
-        <v xml:space="preserve"> TINTO DE VERANO - COPA</v>
+        <v>SANGRIA - JARRA</v>
       </c>
       <c r="C54" t="str">
         <v>.</v>
       </c>
       <c r="D54">
-        <v>18000</v>
+        <v>95000</v>
       </c>
       <c r="F54" t="str">
-        <v>images/productos/1583 menu/Jarra Sangria.JPG</v>
+        <v>images/productos/1583 menu/Media Jarra.JPG</v>
       </c>
     </row>
     <row r="55">
@@ -1301,13 +1301,13 @@
         <v>Vinos</v>
       </c>
       <c r="B55" t="str">
-        <v>SANGRIA - JARRA</v>
+        <v>SANGRIA MEDIA  JARRA</v>
       </c>
       <c r="C55" t="str">
         <v>.</v>
       </c>
       <c r="D55">
-        <v>95000</v>
+        <v>47500</v>
       </c>
       <c r="F55" t="str">
         <v>images/productos/1583 menu/Media Jarra.JPG</v>
@@ -1318,16 +1318,16 @@
         <v>Vinos</v>
       </c>
       <c r="B56" t="str">
-        <v>SANGRIA MEDIA  JARRA</v>
+        <v>COPA - VINO TINTO</v>
       </c>
       <c r="C56" t="str">
         <v>.</v>
       </c>
       <c r="D56">
-        <v>47500</v>
+        <v>22000</v>
       </c>
       <c r="F56" t="str">
-        <v>images/productos/1583 menu/Media Jarra.JPG</v>
+        <v>images/productos/1583 menu/Vino tinto.JPG</v>
       </c>
     </row>
     <row r="57">
@@ -1335,7 +1335,7 @@
         <v>Vinos</v>
       </c>
       <c r="B57" t="str">
-        <v>COPA - VINO TINTO</v>
+        <v>COPA - VINO BLANCO</v>
       </c>
       <c r="C57" t="str">
         <v>.</v>
@@ -1343,22 +1343,22 @@
       <c r="D57">
         <v>22000</v>
       </c>
-      <c r="F57" t="str">
-        <v>images/productos/1583 menu/Vino tinto.JPG</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Vinos</v>
+        <v>Tabla de Quesos</v>
       </c>
       <c r="B58" t="str">
-        <v>COPA - VINO BLANCO</v>
+        <v>TABLA DE QUESOS 1583 -INDIVIDUAL</v>
       </c>
       <c r="C58" t="str">
         <v>.</v>
       </c>
       <c r="D58">
-        <v>22000</v>
+        <v>40000</v>
+      </c>
+      <c r="F58" t="str">
+        <v>images/productos/1583 menu/Tabla de quesos.JPG</v>
       </c>
     </row>
     <row r="59">
@@ -1366,41 +1366,41 @@
         <v>Tabla de Quesos</v>
       </c>
       <c r="B59" t="str">
-        <v>TABLA DE QUESOS 1583 -INDIVIDUAL</v>
+        <v>TABLA DE QUESOS 1583 -COMPARTIR (2 personas)</v>
       </c>
       <c r="C59" t="str">
         <v>.</v>
       </c>
       <c r="D59">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="F59" t="str">
-        <v>images/productos/1583 menu/Tabla de quesos.JPG</v>
+        <v>images/productos/1583 menu/Tabla de queso 2.JPG</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Tabla de Quesos</v>
+        <v>Galletas</v>
       </c>
       <c r="B60" t="str">
-        <v>TABLA DE QUESOS 1583 -COMPARTIR (2 personas)</v>
+        <v>GALLETAS CHIPS DE CHOCOLATE 80 gr</v>
       </c>
       <c r="C60" t="str">
         <v>.</v>
       </c>
       <c r="D60">
-        <v>55000</v>
+        <v>10000</v>
       </c>
       <c r="F60" t="str">
-        <v>images/productos/1583 menu/Tabla de queso 2.JPG</v>
+        <v>images/productos/1583 menu/Galletas.jpg</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Galletas</v>
+        <v>Mousse</v>
       </c>
       <c r="B61" t="str">
-        <v>GALLETAS CHIPS DE CHOCOLATE 80 gr</v>
+        <v>MOUSSE (MARACUYA,LIMON,MORA)</v>
       </c>
       <c r="C61" t="str">
         <v>.</v>
@@ -1408,42 +1408,50 @@
       <c r="D61">
         <v>10000</v>
       </c>
-      <c r="F61" t="str">
-        <v>images/productos/1583 menu/Galletas.jpg</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Mousse</v>
+        <v>By 1583</v>
       </c>
       <c r="B62" t="str">
-        <v>MOUSSE (MARACUYA,LIMON,MORA)</v>
+        <v>MUG</v>
       </c>
       <c r="C62" t="str">
         <v>.</v>
       </c>
       <c r="D62">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>By 1583</v>
+        <v>Bebidas Calientes</v>
       </c>
       <c r="B63" t="str">
-        <v>MUG</v>
+        <v>Shot Baileys 40oz</v>
       </c>
       <c r="C63" t="str">
         <v>.</v>
       </c>
       <c r="D63">
-        <v>20000</v>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Combos</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Capuccino con Wafflebono</v>
+      </c>
+      <c r="D64">
+        <v>16500</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F64"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Cargue productos/Menu Web.xlsx
+++ b/Cargue productos/Menu Web.xlsx
@@ -458,7 +458,7 @@
         <v>Panadería</v>
       </c>
       <c r="B4" t="str">
-        <v>CROISSANT  JAMON Y QUESO  85 G</v>
+        <v>CROISSANT  JAMÓN Y QUESO  85 G</v>
       </c>
       <c r="C4" t="str">
         <v>.</v>
@@ -509,7 +509,7 @@
         <v>Panadería</v>
       </c>
       <c r="B7" t="str">
-        <v>PASTEL TRIPLE CHICHARRON 115 G</v>
+        <v>PASTEL TRIPLE CHICHARRÓN 115 G</v>
       </c>
       <c r="C7" t="str">
         <v>.</v>
@@ -577,7 +577,7 @@
         <v>Panadería</v>
       </c>
       <c r="B11" t="str">
-        <v>Pastel de pollo 100 gr</v>
+        <v>Horneado de pollo 100 gr</v>
       </c>
       <c r="C11" t="str">
         <v>.</v>
@@ -880,7 +880,7 @@
         <v>.</v>
       </c>
       <c r="D29">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="F29" t="str">
         <v>images/productos/1583 menu/Capuccino.png</v>
@@ -1216,7 +1216,7 @@
         <v>Sodas Italianas</v>
       </c>
       <c r="B50" t="str">
-        <v>SODA ITALIANA DE MARACUYA</v>
+        <v>SODA ITALIANA DE MARACUYÁ</v>
       </c>
       <c r="C50" t="str">
         <v>.</v>
@@ -1267,7 +1267,7 @@
         <v>Vinos</v>
       </c>
       <c r="B53" t="str">
-        <v xml:space="preserve"> TINTO DE VERANO - COPA</v>
+        <v>TINTO DE VERANO - COPA</v>
       </c>
       <c r="C53" t="str">
         <v>.</v>
@@ -1301,7 +1301,7 @@
         <v>Vinos</v>
       </c>
       <c r="B55" t="str">
-        <v>SANGRIA MEDIA  JARRA</v>
+        <v>SANGRIA - MEDIA JARRA</v>
       </c>
       <c r="C55" t="str">
         <v>.</v>
@@ -1400,7 +1400,7 @@
         <v>Mousse</v>
       </c>
       <c r="B61" t="str">
-        <v>MOUSSE (MARACUYA,LIMON,MORA)</v>
+        <v>MOUSSE (MARACUYÁ,LIMÓN,MORA)</v>
       </c>
       <c r="C61" t="str">
         <v>.</v>

--- a/Cargue productos/Menu Web.xlsx
+++ b/Cargue productos/Menu Web.xlsx
@@ -1205,7 +1205,7 @@
         <v>.</v>
       </c>
       <c r="D49">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="F49" t="str">
         <v>images/productos/1583 menu/frutos rojos.jpg</v>
@@ -1222,7 +1222,7 @@
         <v>.</v>
       </c>
       <c r="D50">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="F50" t="str">
         <v>images/productos/1583 menu/soda maracuya.jpg</v>

--- a/Cargue productos/Menu Web.xlsx
+++ b/Cargue productos/Menu Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\1583-Menu\Cargue productos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB225CA-21C7-4CB7-961C-A1B910410891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B124277D-99D1-4C0C-8038-021B95AE1DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="11850" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="180">
   <si>
     <t>Categoría</t>
   </si>
@@ -554,6 +554,12 @@
   </si>
   <si>
     <t>Mousse (maracuyá, limón, mora)</t>
+  </si>
+  <si>
+    <t>Nombre Inglés</t>
+  </si>
+  <si>
+    <t>Categoría Inglés</t>
   </si>
 </sst>
 </file>
@@ -913,10 +919,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -935,8 +941,14 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -953,7 +965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -970,7 +982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -987,7 +999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1004,7 +1016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1021,7 +1033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1038,7 +1050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1055,7 +1067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1072,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1086,7 +1098,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1100,7 +1112,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1117,7 +1129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1134,7 +1146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1151,7 +1163,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -1168,7 +1180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>59</v>
       </c>

--- a/Cargue productos/Menu Web.xlsx
+++ b/Cargue productos/Menu Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\1583-Menu\Cargue productos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B124277D-99D1-4C0C-8038-021B95AE1DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DC5F9A-8F6A-427B-8793-E060C52E62FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="180">
   <si>
     <t>Categoría</t>
   </si>
@@ -2410,7 +2410,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>55</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>55</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>55</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>8500</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>6900</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>6900</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>8900</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>56</v>
       </c>
@@ -2627,11 +2627,8 @@
       <c r="D112">
         <v>19900</v>
       </c>
-      <c r="F112" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>56</v>
       </c>
@@ -2644,11 +2641,8 @@
       <c r="D113">
         <v>5000</v>
       </c>
-      <c r="F113" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>56</v>
       </c>
@@ -2662,7 +2656,7 @@
         <v>107000</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -2676,7 +2670,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>56</v>
       </c>
@@ -2690,7 +2684,7 @@
         <v>11900</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>56</v>
       </c>
@@ -2704,7 +2698,7 @@
         <v>11900</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>56</v>
       </c>
@@ -2718,7 +2712,7 @@
         <v>18900</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>56</v>
       </c>
@@ -2732,7 +2726,7 @@
         <v>19900</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>56</v>
       </c>
@@ -2746,7 +2740,7 @@
         <v>21900</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>58</v>
       </c>
@@ -2760,7 +2754,7 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>58</v>
       </c>
@@ -2774,7 +2768,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>54</v>
       </c>
